--- a/artfynd/A 1854-2026 artfynd.xlsx
+++ b/artfynd/A 1854-2026 artfynd.xlsx
@@ -1020,7 +1020,7 @@
         <v>137403907</v>
       </c>
       <c r="B5" t="n">
-        <v>111732</v>
+        <v>111733</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1132,7 +1132,7 @@
         <v>137403909</v>
       </c>
       <c r="B6" t="n">
-        <v>111732</v>
+        <v>111733</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1244,7 +1244,7 @@
         <v>137403953</v>
       </c>
       <c r="B7" t="n">
-        <v>111732</v>
+        <v>111733</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1356,7 +1356,7 @@
         <v>137403902</v>
       </c>
       <c r="B8" t="n">
-        <v>107141</v>
+        <v>107142</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1468,7 +1468,7 @@
         <v>137403908</v>
       </c>
       <c r="B9" t="n">
-        <v>107141</v>
+        <v>107142</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1580,7 +1580,7 @@
         <v>137403935</v>
       </c>
       <c r="B10" t="n">
-        <v>107141</v>
+        <v>107142</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1692,7 +1692,7 @@
         <v>137403952</v>
       </c>
       <c r="B11" t="n">
-        <v>107141</v>
+        <v>107142</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1804,7 +1804,7 @@
         <v>137403955</v>
       </c>
       <c r="B12" t="n">
-        <v>107141</v>
+        <v>107142</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2028,7 +2028,7 @@
         <v>137403919</v>
       </c>
       <c r="B14" t="n">
-        <v>103724</v>
+        <v>103725</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2140,7 +2140,7 @@
         <v>137403920</v>
       </c>
       <c r="B15" t="n">
-        <v>103724</v>
+        <v>103725</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2252,7 +2252,7 @@
         <v>137403921</v>
       </c>
       <c r="B16" t="n">
-        <v>103724</v>
+        <v>103725</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2364,7 +2364,7 @@
         <v>137403922</v>
       </c>
       <c r="B17" t="n">
-        <v>103724</v>
+        <v>103725</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2476,7 +2476,7 @@
         <v>137403923</v>
       </c>
       <c r="B18" t="n">
-        <v>103724</v>
+        <v>103725</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2588,7 +2588,7 @@
         <v>137403924</v>
       </c>
       <c r="B19" t="n">
-        <v>103724</v>
+        <v>103725</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2700,7 +2700,7 @@
         <v>137403925</v>
       </c>
       <c r="B20" t="n">
-        <v>103724</v>
+        <v>103725</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2812,7 +2812,7 @@
         <v>137403926</v>
       </c>
       <c r="B21" t="n">
-        <v>103724</v>
+        <v>103725</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2924,7 +2924,7 @@
         <v>137403927</v>
       </c>
       <c r="B22" t="n">
-        <v>103724</v>
+        <v>103725</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3036,7 +3036,7 @@
         <v>137403928</v>
       </c>
       <c r="B23" t="n">
-        <v>103724</v>
+        <v>103725</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3148,7 +3148,7 @@
         <v>137403929</v>
       </c>
       <c r="B24" t="n">
-        <v>103724</v>
+        <v>103725</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3260,7 +3260,7 @@
         <v>137403930</v>
       </c>
       <c r="B25" t="n">
-        <v>103724</v>
+        <v>103725</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3372,7 +3372,7 @@
         <v>137403931</v>
       </c>
       <c r="B26" t="n">
-        <v>103724</v>
+        <v>103725</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3484,7 +3484,7 @@
         <v>137403933</v>
       </c>
       <c r="B27" t="n">
-        <v>103724</v>
+        <v>103725</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3596,7 +3596,7 @@
         <v>137403934</v>
       </c>
       <c r="B28" t="n">
-        <v>103724</v>
+        <v>103725</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3708,7 +3708,7 @@
         <v>137403936</v>
       </c>
       <c r="B29" t="n">
-        <v>103724</v>
+        <v>103725</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3820,7 +3820,7 @@
         <v>137403937</v>
       </c>
       <c r="B30" t="n">
-        <v>103724</v>
+        <v>103725</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3932,7 +3932,7 @@
         <v>137403938</v>
       </c>
       <c r="B31" t="n">
-        <v>103724</v>
+        <v>103725</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4044,7 +4044,7 @@
         <v>137403940</v>
       </c>
       <c r="B32" t="n">
-        <v>103724</v>
+        <v>103725</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4156,7 +4156,7 @@
         <v>137403941</v>
       </c>
       <c r="B33" t="n">
-        <v>103724</v>
+        <v>103725</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4268,7 +4268,7 @@
         <v>137403942</v>
       </c>
       <c r="B34" t="n">
-        <v>103724</v>
+        <v>103725</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4380,7 +4380,7 @@
         <v>137403943</v>
       </c>
       <c r="B35" t="n">
-        <v>103724</v>
+        <v>103725</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4492,7 +4492,7 @@
         <v>137403944</v>
       </c>
       <c r="B36" t="n">
-        <v>103724</v>
+        <v>103725</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4604,7 +4604,7 @@
         <v>137403945</v>
       </c>
       <c r="B37" t="n">
-        <v>103724</v>
+        <v>103725</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4716,7 +4716,7 @@
         <v>137403946</v>
       </c>
       <c r="B38" t="n">
-        <v>103724</v>
+        <v>103725</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4828,7 +4828,7 @@
         <v>137403947</v>
       </c>
       <c r="B39" t="n">
-        <v>103724</v>
+        <v>103725</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4940,7 +4940,7 @@
         <v>137403948</v>
       </c>
       <c r="B40" t="n">
-        <v>103724</v>
+        <v>103725</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5052,7 +5052,7 @@
         <v>137403949</v>
       </c>
       <c r="B41" t="n">
-        <v>103724</v>
+        <v>103725</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5164,7 +5164,7 @@
         <v>137403954</v>
       </c>
       <c r="B42" t="n">
-        <v>103724</v>
+        <v>103725</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>

--- a/artfynd/A 1854-2026 artfynd.xlsx
+++ b/artfynd/A 1854-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137403917</v>
       </c>
       <c r="B2" t="n">
-        <v>96630</v>
+        <v>96642</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137403900</v>
       </c>
       <c r="B3" t="n">
-        <v>87402</v>
+        <v>87413</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -908,7 +908,7 @@
         <v>137403951</v>
       </c>
       <c r="B4" t="n">
-        <v>92190</v>
+        <v>92202</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1020,7 +1020,7 @@
         <v>137403907</v>
       </c>
       <c r="B5" t="n">
-        <v>111733</v>
+        <v>111745</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1132,7 +1132,7 @@
         <v>137403909</v>
       </c>
       <c r="B6" t="n">
-        <v>111733</v>
+        <v>111745</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1244,7 +1244,7 @@
         <v>137403953</v>
       </c>
       <c r="B7" t="n">
-        <v>111733</v>
+        <v>111745</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1356,7 +1356,7 @@
         <v>137403902</v>
       </c>
       <c r="B8" t="n">
-        <v>107142</v>
+        <v>107154</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1468,7 +1468,7 @@
         <v>137403908</v>
       </c>
       <c r="B9" t="n">
-        <v>107142</v>
+        <v>107154</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1580,7 +1580,7 @@
         <v>137403935</v>
       </c>
       <c r="B10" t="n">
-        <v>107142</v>
+        <v>107154</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1692,7 +1692,7 @@
         <v>137403952</v>
       </c>
       <c r="B11" t="n">
-        <v>107142</v>
+        <v>107154</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1804,7 +1804,7 @@
         <v>137403955</v>
       </c>
       <c r="B12" t="n">
-        <v>107142</v>
+        <v>107154</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1916,7 +1916,7 @@
         <v>137403898</v>
       </c>
       <c r="B13" t="n">
-        <v>101634</v>
+        <v>101646</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2028,7 +2028,7 @@
         <v>137403919</v>
       </c>
       <c r="B14" t="n">
-        <v>103725</v>
+        <v>103737</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2140,7 +2140,7 @@
         <v>137403920</v>
       </c>
       <c r="B15" t="n">
-        <v>103725</v>
+        <v>103737</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2252,7 +2252,7 @@
         <v>137403921</v>
       </c>
       <c r="B16" t="n">
-        <v>103725</v>
+        <v>103737</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2364,7 +2364,7 @@
         <v>137403922</v>
       </c>
       <c r="B17" t="n">
-        <v>103725</v>
+        <v>103737</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2476,7 +2476,7 @@
         <v>137403923</v>
       </c>
       <c r="B18" t="n">
-        <v>103725</v>
+        <v>103737</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2588,7 +2588,7 @@
         <v>137403924</v>
       </c>
       <c r="B19" t="n">
-        <v>103725</v>
+        <v>103737</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2700,7 +2700,7 @@
         <v>137403925</v>
       </c>
       <c r="B20" t="n">
-        <v>103725</v>
+        <v>103737</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2812,7 +2812,7 @@
         <v>137403926</v>
       </c>
       <c r="B21" t="n">
-        <v>103725</v>
+        <v>103737</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2924,7 +2924,7 @@
         <v>137403927</v>
       </c>
       <c r="B22" t="n">
-        <v>103725</v>
+        <v>103737</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3036,7 +3036,7 @@
         <v>137403928</v>
       </c>
       <c r="B23" t="n">
-        <v>103725</v>
+        <v>103737</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3148,7 +3148,7 @@
         <v>137403929</v>
       </c>
       <c r="B24" t="n">
-        <v>103725</v>
+        <v>103737</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3260,7 +3260,7 @@
         <v>137403930</v>
       </c>
       <c r="B25" t="n">
-        <v>103725</v>
+        <v>103737</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3372,7 +3372,7 @@
         <v>137403931</v>
       </c>
       <c r="B26" t="n">
-        <v>103725</v>
+        <v>103737</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3484,7 +3484,7 @@
         <v>137403933</v>
       </c>
       <c r="B27" t="n">
-        <v>103725</v>
+        <v>103737</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3596,7 +3596,7 @@
         <v>137403934</v>
       </c>
       <c r="B28" t="n">
-        <v>103725</v>
+        <v>103737</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3708,7 +3708,7 @@
         <v>137403936</v>
       </c>
       <c r="B29" t="n">
-        <v>103725</v>
+        <v>103737</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3820,7 +3820,7 @@
         <v>137403937</v>
       </c>
       <c r="B30" t="n">
-        <v>103725</v>
+        <v>103737</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3932,7 +3932,7 @@
         <v>137403938</v>
       </c>
       <c r="B31" t="n">
-        <v>103725</v>
+        <v>103737</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4044,7 +4044,7 @@
         <v>137403940</v>
       </c>
       <c r="B32" t="n">
-        <v>103725</v>
+        <v>103737</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4156,7 +4156,7 @@
         <v>137403941</v>
       </c>
       <c r="B33" t="n">
-        <v>103725</v>
+        <v>103737</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4268,7 +4268,7 @@
         <v>137403942</v>
       </c>
       <c r="B34" t="n">
-        <v>103725</v>
+        <v>103737</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4380,7 +4380,7 @@
         <v>137403943</v>
       </c>
       <c r="B35" t="n">
-        <v>103725</v>
+        <v>103737</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4492,7 +4492,7 @@
         <v>137403944</v>
       </c>
       <c r="B36" t="n">
-        <v>103725</v>
+        <v>103737</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4604,7 +4604,7 @@
         <v>137403945</v>
       </c>
       <c r="B37" t="n">
-        <v>103725</v>
+        <v>103737</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4716,7 +4716,7 @@
         <v>137403946</v>
       </c>
       <c r="B38" t="n">
-        <v>103725</v>
+        <v>103737</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4828,7 +4828,7 @@
         <v>137403947</v>
       </c>
       <c r="B39" t="n">
-        <v>103725</v>
+        <v>103737</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4940,7 +4940,7 @@
         <v>137403948</v>
       </c>
       <c r="B40" t="n">
-        <v>103725</v>
+        <v>103737</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5052,7 +5052,7 @@
         <v>137403949</v>
       </c>
       <c r="B41" t="n">
-        <v>103725</v>
+        <v>103737</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5164,7 +5164,7 @@
         <v>137403954</v>
       </c>
       <c r="B42" t="n">
-        <v>103725</v>
+        <v>103737</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>

--- a/artfynd/A 1854-2026 artfynd.xlsx
+++ b/artfynd/A 1854-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137403917</v>
       </c>
       <c r="B2" t="n">
-        <v>96642</v>
+        <v>96643</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137403900</v>
       </c>
       <c r="B3" t="n">
-        <v>87413</v>
+        <v>87414</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -908,7 +908,7 @@
         <v>137403951</v>
       </c>
       <c r="B4" t="n">
-        <v>92202</v>
+        <v>92203</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1020,7 +1020,7 @@
         <v>137403907</v>
       </c>
       <c r="B5" t="n">
-        <v>111745</v>
+        <v>111746</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1132,7 +1132,7 @@
         <v>137403909</v>
       </c>
       <c r="B6" t="n">
-        <v>111745</v>
+        <v>111746</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1244,7 +1244,7 @@
         <v>137403953</v>
       </c>
       <c r="B7" t="n">
-        <v>111745</v>
+        <v>111746</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1356,7 +1356,7 @@
         <v>137403902</v>
       </c>
       <c r="B8" t="n">
-        <v>107154</v>
+        <v>107155</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1468,7 +1468,7 @@
         <v>137403908</v>
       </c>
       <c r="B9" t="n">
-        <v>107154</v>
+        <v>107155</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1580,7 +1580,7 @@
         <v>137403935</v>
       </c>
       <c r="B10" t="n">
-        <v>107154</v>
+        <v>107155</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1692,7 +1692,7 @@
         <v>137403952</v>
       </c>
       <c r="B11" t="n">
-        <v>107154</v>
+        <v>107155</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1804,7 +1804,7 @@
         <v>137403955</v>
       </c>
       <c r="B12" t="n">
-        <v>107154</v>
+        <v>107155</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1916,7 +1916,7 @@
         <v>137403898</v>
       </c>
       <c r="B13" t="n">
-        <v>101646</v>
+        <v>101647</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2028,7 +2028,7 @@
         <v>137403919</v>
       </c>
       <c r="B14" t="n">
-        <v>103737</v>
+        <v>103738</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2140,7 +2140,7 @@
         <v>137403920</v>
       </c>
       <c r="B15" t="n">
-        <v>103737</v>
+        <v>103738</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2252,7 +2252,7 @@
         <v>137403921</v>
       </c>
       <c r="B16" t="n">
-        <v>103737</v>
+        <v>103738</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2364,7 +2364,7 @@
         <v>137403922</v>
       </c>
       <c r="B17" t="n">
-        <v>103737</v>
+        <v>103738</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2476,7 +2476,7 @@
         <v>137403923</v>
       </c>
       <c r="B18" t="n">
-        <v>103737</v>
+        <v>103738</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2588,7 +2588,7 @@
         <v>137403924</v>
       </c>
       <c r="B19" t="n">
-        <v>103737</v>
+        <v>103738</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2700,7 +2700,7 @@
         <v>137403925</v>
       </c>
       <c r="B20" t="n">
-        <v>103737</v>
+        <v>103738</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2812,7 +2812,7 @@
         <v>137403926</v>
       </c>
       <c r="B21" t="n">
-        <v>103737</v>
+        <v>103738</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2924,7 +2924,7 @@
         <v>137403927</v>
       </c>
       <c r="B22" t="n">
-        <v>103737</v>
+        <v>103738</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3036,7 +3036,7 @@
         <v>137403928</v>
       </c>
       <c r="B23" t="n">
-        <v>103737</v>
+        <v>103738</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3148,7 +3148,7 @@
         <v>137403929</v>
       </c>
       <c r="B24" t="n">
-        <v>103737</v>
+        <v>103738</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3260,7 +3260,7 @@
         <v>137403930</v>
       </c>
       <c r="B25" t="n">
-        <v>103737</v>
+        <v>103738</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3372,7 +3372,7 @@
         <v>137403931</v>
       </c>
       <c r="B26" t="n">
-        <v>103737</v>
+        <v>103738</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3484,7 +3484,7 @@
         <v>137403933</v>
       </c>
       <c r="B27" t="n">
-        <v>103737</v>
+        <v>103738</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3596,7 +3596,7 @@
         <v>137403934</v>
       </c>
       <c r="B28" t="n">
-        <v>103737</v>
+        <v>103738</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3708,7 +3708,7 @@
         <v>137403936</v>
       </c>
       <c r="B29" t="n">
-        <v>103737</v>
+        <v>103738</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3820,7 +3820,7 @@
         <v>137403937</v>
       </c>
       <c r="B30" t="n">
-        <v>103737</v>
+        <v>103738</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3932,7 +3932,7 @@
         <v>137403938</v>
       </c>
       <c r="B31" t="n">
-        <v>103737</v>
+        <v>103738</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4044,7 +4044,7 @@
         <v>137403940</v>
       </c>
       <c r="B32" t="n">
-        <v>103737</v>
+        <v>103738</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4156,7 +4156,7 @@
         <v>137403941</v>
       </c>
       <c r="B33" t="n">
-        <v>103737</v>
+        <v>103738</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4268,7 +4268,7 @@
         <v>137403942</v>
       </c>
       <c r="B34" t="n">
-        <v>103737</v>
+        <v>103738</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4380,7 +4380,7 @@
         <v>137403943</v>
       </c>
       <c r="B35" t="n">
-        <v>103737</v>
+        <v>103738</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4492,7 +4492,7 @@
         <v>137403944</v>
       </c>
       <c r="B36" t="n">
-        <v>103737</v>
+        <v>103738</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4604,7 +4604,7 @@
         <v>137403945</v>
       </c>
       <c r="B37" t="n">
-        <v>103737</v>
+        <v>103738</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4716,7 +4716,7 @@
         <v>137403946</v>
       </c>
       <c r="B38" t="n">
-        <v>103737</v>
+        <v>103738</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4828,7 +4828,7 @@
         <v>137403947</v>
       </c>
       <c r="B39" t="n">
-        <v>103737</v>
+        <v>103738</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4940,7 +4940,7 @@
         <v>137403948</v>
       </c>
       <c r="B40" t="n">
-        <v>103737</v>
+        <v>103738</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5052,7 +5052,7 @@
         <v>137403949</v>
       </c>
       <c r="B41" t="n">
-        <v>103737</v>
+        <v>103738</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5164,7 +5164,7 @@
         <v>137403954</v>
       </c>
       <c r="B42" t="n">
-        <v>103737</v>
+        <v>103738</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>

--- a/artfynd/A 1854-2026 artfynd.xlsx
+++ b/artfynd/A 1854-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137403917</v>
       </c>
       <c r="B2" t="n">
-        <v>96643</v>
+        <v>96646</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137403900</v>
       </c>
       <c r="B3" t="n">
-        <v>87414</v>
+        <v>87417</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -908,7 +908,7 @@
         <v>137403951</v>
       </c>
       <c r="B4" t="n">
-        <v>92203</v>
+        <v>92206</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1020,7 +1020,7 @@
         <v>137403907</v>
       </c>
       <c r="B5" t="n">
-        <v>111746</v>
+        <v>111749</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1132,7 +1132,7 @@
         <v>137403909</v>
       </c>
       <c r="B6" t="n">
-        <v>111746</v>
+        <v>111749</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1244,7 +1244,7 @@
         <v>137403953</v>
       </c>
       <c r="B7" t="n">
-        <v>111746</v>
+        <v>111749</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1356,7 +1356,7 @@
         <v>137403902</v>
       </c>
       <c r="B8" t="n">
-        <v>107155</v>
+        <v>107158</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1468,7 +1468,7 @@
         <v>137403908</v>
       </c>
       <c r="B9" t="n">
-        <v>107155</v>
+        <v>107158</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1580,7 +1580,7 @@
         <v>137403935</v>
       </c>
       <c r="B10" t="n">
-        <v>107155</v>
+        <v>107158</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1692,7 +1692,7 @@
         <v>137403952</v>
       </c>
       <c r="B11" t="n">
-        <v>107155</v>
+        <v>107158</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1804,7 +1804,7 @@
         <v>137403955</v>
       </c>
       <c r="B12" t="n">
-        <v>107155</v>
+        <v>107158</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1916,7 +1916,7 @@
         <v>137403898</v>
       </c>
       <c r="B13" t="n">
-        <v>101647</v>
+        <v>101650</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2028,7 +2028,7 @@
         <v>137403919</v>
       </c>
       <c r="B14" t="n">
-        <v>103738</v>
+        <v>103741</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2140,7 +2140,7 @@
         <v>137403920</v>
       </c>
       <c r="B15" t="n">
-        <v>103738</v>
+        <v>103741</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2252,7 +2252,7 @@
         <v>137403921</v>
       </c>
       <c r="B16" t="n">
-        <v>103738</v>
+        <v>103741</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2364,7 +2364,7 @@
         <v>137403922</v>
       </c>
       <c r="B17" t="n">
-        <v>103738</v>
+        <v>103741</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2476,7 +2476,7 @@
         <v>137403923</v>
       </c>
       <c r="B18" t="n">
-        <v>103738</v>
+        <v>103741</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2588,7 +2588,7 @@
         <v>137403924</v>
       </c>
       <c r="B19" t="n">
-        <v>103738</v>
+        <v>103741</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2700,7 +2700,7 @@
         <v>137403925</v>
       </c>
       <c r="B20" t="n">
-        <v>103738</v>
+        <v>103741</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2812,7 +2812,7 @@
         <v>137403926</v>
       </c>
       <c r="B21" t="n">
-        <v>103738</v>
+        <v>103741</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2924,7 +2924,7 @@
         <v>137403927</v>
       </c>
       <c r="B22" t="n">
-        <v>103738</v>
+        <v>103741</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3036,7 +3036,7 @@
         <v>137403928</v>
       </c>
       <c r="B23" t="n">
-        <v>103738</v>
+        <v>103741</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3148,7 +3148,7 @@
         <v>137403929</v>
       </c>
       <c r="B24" t="n">
-        <v>103738</v>
+        <v>103741</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3260,7 +3260,7 @@
         <v>137403930</v>
       </c>
       <c r="B25" t="n">
-        <v>103738</v>
+        <v>103741</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3372,7 +3372,7 @@
         <v>137403931</v>
       </c>
       <c r="B26" t="n">
-        <v>103738</v>
+        <v>103741</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3484,7 +3484,7 @@
         <v>137403933</v>
       </c>
       <c r="B27" t="n">
-        <v>103738</v>
+        <v>103741</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3596,7 +3596,7 @@
         <v>137403934</v>
       </c>
       <c r="B28" t="n">
-        <v>103738</v>
+        <v>103741</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3708,7 +3708,7 @@
         <v>137403936</v>
       </c>
       <c r="B29" t="n">
-        <v>103738</v>
+        <v>103741</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3820,7 +3820,7 @@
         <v>137403937</v>
       </c>
       <c r="B30" t="n">
-        <v>103738</v>
+        <v>103741</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3932,7 +3932,7 @@
         <v>137403938</v>
       </c>
       <c r="B31" t="n">
-        <v>103738</v>
+        <v>103741</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4044,7 +4044,7 @@
         <v>137403940</v>
       </c>
       <c r="B32" t="n">
-        <v>103738</v>
+        <v>103741</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4156,7 +4156,7 @@
         <v>137403941</v>
       </c>
       <c r="B33" t="n">
-        <v>103738</v>
+        <v>103741</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4268,7 +4268,7 @@
         <v>137403942</v>
       </c>
       <c r="B34" t="n">
-        <v>103738</v>
+        <v>103741</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4380,7 +4380,7 @@
         <v>137403943</v>
       </c>
       <c r="B35" t="n">
-        <v>103738</v>
+        <v>103741</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4492,7 +4492,7 @@
         <v>137403944</v>
       </c>
       <c r="B36" t="n">
-        <v>103738</v>
+        <v>103741</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4604,7 +4604,7 @@
         <v>137403945</v>
       </c>
       <c r="B37" t="n">
-        <v>103738</v>
+        <v>103741</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4716,7 +4716,7 @@
         <v>137403946</v>
       </c>
       <c r="B38" t="n">
-        <v>103738</v>
+        <v>103741</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4828,7 +4828,7 @@
         <v>137403947</v>
       </c>
       <c r="B39" t="n">
-        <v>103738</v>
+        <v>103741</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4940,7 +4940,7 @@
         <v>137403948</v>
       </c>
       <c r="B40" t="n">
-        <v>103738</v>
+        <v>103741</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5052,7 +5052,7 @@
         <v>137403949</v>
       </c>
       <c r="B41" t="n">
-        <v>103738</v>
+        <v>103741</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5164,7 +5164,7 @@
         <v>137403954</v>
       </c>
       <c r="B42" t="n">
-        <v>103738</v>
+        <v>103741</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>

--- a/artfynd/A 1854-2026 artfynd.xlsx
+++ b/artfynd/A 1854-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137403917</v>
       </c>
       <c r="B2" t="n">
-        <v>96646</v>
+        <v>96650</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137403900</v>
       </c>
       <c r="B3" t="n">
-        <v>87417</v>
+        <v>87421</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -908,7 +908,7 @@
         <v>137403951</v>
       </c>
       <c r="B4" t="n">
-        <v>92206</v>
+        <v>92210</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1020,7 +1020,7 @@
         <v>137403907</v>
       </c>
       <c r="B5" t="n">
-        <v>111749</v>
+        <v>111755</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1132,7 +1132,7 @@
         <v>137403909</v>
       </c>
       <c r="B6" t="n">
-        <v>111749</v>
+        <v>111755</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1244,7 +1244,7 @@
         <v>137403953</v>
       </c>
       <c r="B7" t="n">
-        <v>111749</v>
+        <v>111755</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1356,7 +1356,7 @@
         <v>137403902</v>
       </c>
       <c r="B8" t="n">
-        <v>107158</v>
+        <v>107164</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1468,7 +1468,7 @@
         <v>137403908</v>
       </c>
       <c r="B9" t="n">
-        <v>107158</v>
+        <v>107164</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1580,7 +1580,7 @@
         <v>137403935</v>
       </c>
       <c r="B10" t="n">
-        <v>107158</v>
+        <v>107164</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1692,7 +1692,7 @@
         <v>137403952</v>
       </c>
       <c r="B11" t="n">
-        <v>107158</v>
+        <v>107164</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1804,7 +1804,7 @@
         <v>137403955</v>
       </c>
       <c r="B12" t="n">
-        <v>107158</v>
+        <v>107164</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1916,7 +1916,7 @@
         <v>137403898</v>
       </c>
       <c r="B13" t="n">
-        <v>101650</v>
+        <v>101654</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2028,7 +2028,7 @@
         <v>137403919</v>
       </c>
       <c r="B14" t="n">
-        <v>103741</v>
+        <v>103746</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2140,7 +2140,7 @@
         <v>137403920</v>
       </c>
       <c r="B15" t="n">
-        <v>103741</v>
+        <v>103746</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2252,7 +2252,7 @@
         <v>137403921</v>
       </c>
       <c r="B16" t="n">
-        <v>103741</v>
+        <v>103746</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2364,7 +2364,7 @@
         <v>137403922</v>
       </c>
       <c r="B17" t="n">
-        <v>103741</v>
+        <v>103746</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2476,7 +2476,7 @@
         <v>137403923</v>
       </c>
       <c r="B18" t="n">
-        <v>103741</v>
+        <v>103746</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2588,7 +2588,7 @@
         <v>137403924</v>
       </c>
       <c r="B19" t="n">
-        <v>103741</v>
+        <v>103746</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2700,7 +2700,7 @@
         <v>137403925</v>
       </c>
       <c r="B20" t="n">
-        <v>103741</v>
+        <v>103746</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2812,7 +2812,7 @@
         <v>137403926</v>
       </c>
       <c r="B21" t="n">
-        <v>103741</v>
+        <v>103746</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2924,7 +2924,7 @@
         <v>137403927</v>
       </c>
       <c r="B22" t="n">
-        <v>103741</v>
+        <v>103746</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3036,7 +3036,7 @@
         <v>137403928</v>
       </c>
       <c r="B23" t="n">
-        <v>103741</v>
+        <v>103746</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3148,7 +3148,7 @@
         <v>137403929</v>
       </c>
       <c r="B24" t="n">
-        <v>103741</v>
+        <v>103746</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3260,7 +3260,7 @@
         <v>137403930</v>
       </c>
       <c r="B25" t="n">
-        <v>103741</v>
+        <v>103746</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3372,7 +3372,7 @@
         <v>137403931</v>
       </c>
       <c r="B26" t="n">
-        <v>103741</v>
+        <v>103746</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3484,7 +3484,7 @@
         <v>137403933</v>
       </c>
       <c r="B27" t="n">
-        <v>103741</v>
+        <v>103746</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3596,7 +3596,7 @@
         <v>137403934</v>
       </c>
       <c r="B28" t="n">
-        <v>103741</v>
+        <v>103746</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3708,7 +3708,7 @@
         <v>137403936</v>
       </c>
       <c r="B29" t="n">
-        <v>103741</v>
+        <v>103746</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3820,7 +3820,7 @@
         <v>137403937</v>
       </c>
       <c r="B30" t="n">
-        <v>103741</v>
+        <v>103746</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3932,7 +3932,7 @@
         <v>137403938</v>
       </c>
       <c r="B31" t="n">
-        <v>103741</v>
+        <v>103746</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4044,7 +4044,7 @@
         <v>137403940</v>
       </c>
       <c r="B32" t="n">
-        <v>103741</v>
+        <v>103746</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4156,7 +4156,7 @@
         <v>137403941</v>
       </c>
       <c r="B33" t="n">
-        <v>103741</v>
+        <v>103746</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4268,7 +4268,7 @@
         <v>137403942</v>
       </c>
       <c r="B34" t="n">
-        <v>103741</v>
+        <v>103746</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4380,7 +4380,7 @@
         <v>137403943</v>
       </c>
       <c r="B35" t="n">
-        <v>103741</v>
+        <v>103746</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4492,7 +4492,7 @@
         <v>137403944</v>
       </c>
       <c r="B36" t="n">
-        <v>103741</v>
+        <v>103746</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4604,7 +4604,7 @@
         <v>137403945</v>
       </c>
       <c r="B37" t="n">
-        <v>103741</v>
+        <v>103746</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4716,7 +4716,7 @@
         <v>137403946</v>
       </c>
       <c r="B38" t="n">
-        <v>103741</v>
+        <v>103746</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4828,7 +4828,7 @@
         <v>137403947</v>
       </c>
       <c r="B39" t="n">
-        <v>103741</v>
+        <v>103746</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4940,7 +4940,7 @@
         <v>137403948</v>
       </c>
       <c r="B40" t="n">
-        <v>103741</v>
+        <v>103746</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5052,7 +5052,7 @@
         <v>137403949</v>
       </c>
       <c r="B41" t="n">
-        <v>103741</v>
+        <v>103746</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5164,7 +5164,7 @@
         <v>137403954</v>
       </c>
       <c r="B42" t="n">
-        <v>103741</v>
+        <v>103746</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
